--- a/input/mapping/005. OCB_GOLD_TCKH_V_CREDIT_LIMIT_BAOANH.xlsx
+++ b/input/mapping/005. OCB_GOLD_TCKH_V_CREDIT_LIMIT_BAOANH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/THAO C/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1286" documentId="13_ncr:1_{069767A0-9E1E-41C0-925B-2DC64A52E7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7CA540B-FDA8-4AD1-9626-75106F293E53}"/>
+  <xr:revisionPtr revIDLastSave="1311" documentId="13_ncr:1_{069767A0-9E1E-41C0-925B-2DC64A52E7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47217F7E-7297-4496-8FD7-F00AF129562E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Code mới </t>
   </si>
   <si>
-    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+    <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
 CREATE OR REPLACE VIEW V_CREDIT_LIMIT AS
 WITH calendar_dates AS (
@@ -150,6 +150,7 @@
     FROM calendar_dates c
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_limit') h
         ON h.source_event_date &lt;= c.data_date
+    WHERE h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
 ),
 limit_sts_del_by_date AS (
     -- Với mỗi ngày snapshot: hashkey có trạng thái mới nhất (&lt;= ngày đó) = 'D'
@@ -160,6 +161,7 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.sts_hub_limit') sts
         ON sts.limit_hashkey = h.limit_hashkey
        AND sts.source_event_date &lt;= h.data_date
+    WHERE sts.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY h.data_date_id, h.limit_hashkey
     HAVING max_by(sts.cdc_status, sts.source_event_date) = 'D'
 ),
@@ -190,6 +192,7 @@
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_limit_information') s
         ON s.limit_hashkey = h.limit_hashkey
        AND s.source_event_date &lt;= h.data_date
+       AND s.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY h.data_date_id, h.limit_hashkey
 )
 SELECT
@@ -200,8 +203,7 @@
 LEFT JOIN limit_sat_by_date x
     ON  x.data_date_id  = a.data_date_id
     AND x.limit_hashkey = a.limit_hashkey
-;
-</t>
+;</t>
   </si>
   <si>
     <t>V_CREDIT_LIMIT - VIEW
@@ -788,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -868,6 +870,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -926,27 +952,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1338,34 +1343,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:13" ht="8.25" customHeight="1"/>
     <row r="3" spans="1:13" ht="24" customHeight="1">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="57"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="57"/>
+      <c r="F3" s="38"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="62" t="s">
+      <c r="H3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="63"/>
+      <c r="I3" s="44"/>
     </row>
     <row r="4" spans="1:13" s="12" customFormat="1" ht="10.5" customHeight="1">
       <c r="B4" s="13"/>
@@ -1378,99 +1383,99 @@
       <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1">
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="48" t="s">
+      <c r="C5" s="59"/>
+      <c r="D5" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="51"/>
-      <c r="G5" s="47" t="s">
+      <c r="F5" s="59"/>
+      <c r="G5" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="42"/>
+      <c r="I5" s="50"/>
     </row>
     <row r="6" spans="1:13" ht="26.25" customHeight="1">
-      <c r="B6" s="52"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="52"/>
     </row>
     <row r="7" spans="1:13" ht="12.75" customHeight="1">
-      <c r="B7" s="52"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="53"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="61"/>
       <c r="G7" s="9"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="26.25" customHeight="1">
-      <c r="B8" s="52"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="48" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="42"/>
+      <c r="I8" s="50"/>
     </row>
     <row r="9" spans="1:13" ht="19.5" customHeight="1">
-      <c r="B9" s="52"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="52"/>
     </row>
     <row r="10" spans="1:13" ht="10.5" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="53"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="1:13" ht="17.25" customHeight="1">
-      <c r="B11" s="52"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="48" t="s">
+      <c r="B11" s="60"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="42"/>
+      <c r="I11" s="50"/>
     </row>
     <row r="12" spans="1:13" ht="17.25" customHeight="1">
-      <c r="B12" s="54"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="52"/>
     </row>
     <row r="13" spans="1:13" ht="12" customHeight="1"/>
     <row r="14" spans="1:13" ht="21.75" customHeight="1">
@@ -1480,12 +1485,12 @@
     </row>
     <row r="15" spans="1:13" ht="20.25" customHeight="1">
       <c r="B15" s="4"/>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -1501,14 +1506,14 @@
       <c r="E16" s="34"/>
       <c r="F16" s="34"/>
       <c r="G16" s="31"/>
-      <c r="H16" s="60" t="s">
+      <c r="H16" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="38" t="s">
+      <c r="I16" s="41"/>
+      <c r="J16" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="K16" s="39"/>
+      <c r="K16" s="47"/>
       <c r="L16" s="36" t="s">
         <v>15</v>
       </c>
@@ -1523,14 +1528,14 @@
       <c r="E17" s="34"/>
       <c r="F17" s="34"/>
       <c r="G17" s="31"/>
-      <c r="H17" s="61" t="s">
+      <c r="H17" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="61"/>
-      <c r="J17" s="37" t="s">
+      <c r="I17" s="42"/>
+      <c r="J17" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="K17" s="37"/>
+      <c r="K17" s="45"/>
       <c r="L17" s="33" t="s">
         <v>18</v>
       </c>
@@ -1590,12 +1595,6 @@
     <row r="43" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="C15:F15"/>
@@ -1608,6 +1607,12 @@
     <mergeCell ref="H11:I12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="D5:D12"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1665,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BDB56BD-E0FB-40C7-B0E7-2507A5594828}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="18" customWidth="1"/>
@@ -1677,13 +1682,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:5" ht="27" customHeight="1">
       <c r="A2" s="21" t="s">
@@ -1819,13 +1824,13 @@
       <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="68"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="69"/>
     </row>
     <row r="12" spans="1:5" ht="18.75" customHeight="1">
       <c r="A12" s="21" t="s">
@@ -1894,6 +1899,9 @@
       <c r="E15" s="23" t="s">
         <v>54</v>
       </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1914,6 +1922,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2085,24 +2103,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE68820-F34F-4A76-8313-DA7B7A088686}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF136867-B022-43DC-91E9-6E5DA7D9B184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ECE3D62-FB22-48EF-9CF6-0B6C6C55E6FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ECE3D62-FB22-48EF-9CF6-0B6C6C55E6FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF136867-B022-43DC-91E9-6E5DA7D9B184}"/>
 </file>
--- a/input/mapping/005. OCB_GOLD_TCKH_V_CREDIT_LIMIT_BAOANH.xlsx
+++ b/input/mapping/005. OCB_GOLD_TCKH_V_CREDIT_LIMIT_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/THAO C/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1311" documentId="13_ncr:1_{069767A0-9E1E-41C0-925B-2DC64A52E7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47217F7E-7297-4496-8FD7-F00AF129562E}"/>
+  <xr:revisionPtr revIDLastSave="1331" documentId="13_ncr:1_{069767A0-9E1E-41C0-925B-2DC64A52E7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A59FD105-0107-4361-B5A6-FCAA736A823C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1913,15 +1913,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -1931,7 +1922,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2103,14 +2094,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE68820-F34F-4A76-8313-DA7B7A088686}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ECE3D62-FB22-48EF-9CF6-0B6C6C55E6FC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ECE3D62-FB22-48EF-9CF6-0B6C6C55E6FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF136867-B022-43DC-91E9-6E5DA7D9B184}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF136867-B022-43DC-91E9-6E5DA7D9B184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE68820-F34F-4A76-8313-DA7B7A088686}"/>
 </file>